--- a/猪眼参数.xlsx
+++ b/猪眼参数.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>论文标题</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>专门测巩膜，取大猪数据（&gt;=27kg）</t>
+  </si>
+  <si>
+    <t>论文给屈光度，换算成曲率半径</t>
   </si>
   <si>
     <t>参数</t>
@@ -139,13 +142,13 @@
     <t>830–1250（未区分前后）</t>
   </si>
   <si>
-    <t>角膜缘后6 mm，厚度0.43±0.16 mm</t>
+    <t>角膜缘厚度1.12±0.23</t>
   </si>
   <si>
     <t>后巩膜厚度</t>
   </si>
   <si>
-    <t>赤道部0.86±0.18 mm，往后趋于平稳</t>
+    <t>赤道部0.86±0.18，往后趋于平稳</t>
   </si>
 </sst>
 </file>
@@ -780,7 +783,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -801,9 +804,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1159,132 +1159,135 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>8.45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" ht="84" spans="1:5">
       <c r="A11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="7">
+        <v>29</v>
+      </c>
+      <c r="C11" s="4">
         <v>2.35</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="7">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4">
         <v>3.5</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
